--- a/reports/pdf_weekly_20260814.xlsx
+++ b/reports/pdf_weekly_20260814.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +562,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>주간 변화  ·  2026-08-10 ~ 2026-08-14  (5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>주간 변화  ·  2026-08-10 ~ 2026-08-14  (5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,744억   ·   현금 263억(5.4%)      주말 2026-08-14  vs  주초 2026-08-10      매수 11종목  /  매도 11종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,744억   ·   현금 260억(5.3%)      주말 2026-08-14  vs  주초 2026-08-10      매수 11종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,11 +665,11 @@
         <v>244</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2871128480</v>
+        <v>2825715200</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.63%</t>
+          <t>0.00%→0.61%</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -686,11 +686,11 @@
         <v>-285</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2943953100</v>
+        <v>-3050041500</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>1.67%→1.02%</t>
+          <t>1.67%→1.04%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
@@ -709,11 +709,11 @@
         <v>84</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>977998560</v>
+        <v>959758800</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>1.81%→1.90%</t>
+          <t>1.81%→1.85%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -730,7 +730,7 @@
         <v>-57</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1874228400</v>
+        <v>-1880122200</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -746,23 +746,23 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>931530600</v>
+        <v>4280760000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.29%→0.49%</t>
+          <t>0.99%→1.93%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>47→80</t>
+          <t>75→144</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -774,11 +774,11 @@
         <v>-35</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-2352350000</v>
+        <v>-2279970000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.99%→0.53%</t>
+          <t>0.99%→0.51%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
@@ -790,23 +790,23 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>436896020</v>
+        <v>952003800</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.96%→1.07%</t>
+          <t>0.29%→0.50%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>318→349</t>
+          <t>47→80</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -818,11 +818,11 @@
         <v>-33</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-3569161200</v>
+        <v>-3610107600</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>5.85%→4.34%</t>
+          <t>5.85%→4.35%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
@@ -834,23 +834,23 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>한국피아이엠  (신규)</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1958085800</v>
+        <v>433370080</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.43%</t>
+          <t>0.96%→1.05%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>0→29</t>
+          <t>318→349</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -859,63 +859,63 @@
         </is>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-13</v>
+        <v>-31</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-341426800</v>
+        <v>-775706800</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.21%</t>
+          <t>0.28%→0.10%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>49→36</t>
+          <t>49→18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>한국피아이엠  (신규)</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1507778800</v>
+        <v>1889118000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.99%→1.40%</t>
+          <t>0.00%→0.41%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>75→98</t>
+          <t>0→29</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-13</v>
+        <v>-19</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-211173820</v>
+        <v>-1862440800</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.05%</t>
+          <t>1.08%→0.66%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>26→13</t>
+          <t>50→31</t>
         </is>
       </c>
     </row>
@@ -929,11 +929,11 @@
         <v>17</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>847259600</v>
+        <v>973821200</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>1.27%→1.26%</t>
+          <t>1.27%→1.44%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
@@ -943,23 +943,23 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2158992000</v>
+        <v>-956967000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.78%→0.51%</t>
+          <t>0.78%→0.55%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>25→13</t>
+          <t>55→40</t>
         </is>
       </c>
     </row>
@@ -973,11 +973,11 @@
         <v>16</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1439328000</v>
+        <v>1460835200</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>2.77%→3.25%</t>
+          <t>2.77%→3.27%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -987,23 +987,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-984368000</v>
+        <v>-202705360</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>1.08%→0.86%</t>
+          <t>0.10%→0.04%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>50→40</t>
+          <t>26→13</t>
         </is>
       </c>
     </row>
@@ -1031,979 +1031,1041 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>원익IPS  (편출)</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-821719800</v>
+        <v>-2224754400</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.19%→0.00%</t>
+          <t>0.78%→0.52%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>9→0</t>
+          <t>25→13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1641475000</v>
+        <v>2142448000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>5.61%→5.72%</t>
+          <t>2.33%→3.12%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>75→80</t>
+          <t>46→54</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-301928000</v>
+        <v>-1305321600</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.69%→0.61%</t>
+          <t>3.87%→3.66%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>82→74</t>
+          <t>168→156</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>775500000</v>
+        <v>1641475000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>2.33%→2.76%</t>
+          <t>5.61%→5.67%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>46→49</t>
+          <t>75→80</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
+          <t>원익IPS  (편출)</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>-821719800</v>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>0.19%→0.00%</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>9→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>한중엔시에스</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>-303168800</v>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>0.69%→0.61%</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>82→74</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>-555154600</v>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>0.36%→0.26%</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>22→15</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
           <t>로보티즈</t>
         </is>
       </c>
-      <c r="H16" s="15" t="n">
+      <c r="H19" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I16" s="15" t="n">
-        <v>-767745000</v>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>3.26%→3.07%</t>
-        </is>
-      </c>
-      <c r="K16" s="13" t="inlineStr">
+      <c r="I19" s="15" t="n">
+        <v>-809622000</v>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>3.26%→3.21%</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
         <is>
           <t>58→55</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,037억   ·   현금 21억(0.5%)      주말 2026-08-14  vs  주초 2026-08-10      매수 7종목  /  매도 4종목</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>큐라클</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n">
-        <v>106</v>
-      </c>
-      <c r="C21" s="11" t="n">
-        <v>657420480</v>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>1.33%→1.68%</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>986→1,092</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>리가켐바이오</t>
-        </is>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>-33</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>-2016897300</v>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>5.60%→5.01%</t>
-        </is>
-      </c>
-      <c r="K21" s="13" t="inlineStr">
-        <is>
-          <t>363→330</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>앱클론</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n">
-        <v>71</v>
-      </c>
-      <c r="C22" s="11" t="n">
-        <v>1164960900</v>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>2.07%→2.50%</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>542→613</t>
-        </is>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>알테오젠</t>
-        </is>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v>-2697480000</v>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>10.07%→9.46%</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="inlineStr">
-        <is>
-          <t>242→226</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>오스코텍</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="n">
-        <v>63</v>
-      </c>
-      <c r="C23" s="11" t="n">
-        <v>1297976400</v>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>3.11%→3.66%</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>652→715</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>-11</v>
-      </c>
-      <c r="I23" s="15" t="n">
-        <v>-1179882000</v>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>8.07%→7.62%</t>
-        </is>
-      </c>
-      <c r="K23" s="13" t="inlineStr">
-        <is>
-          <t>297→286</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>HLB이노베이션</t>
+          <t>큐라클</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>421083000</v>
+        <v>682186320</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>1.71%→1.93%</t>
+          <t>1.33%→1.73%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>1,066→1,127</t>
+          <t>986→1,092</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-7</v>
+        <v>-33</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1471932000</v>
+        <v>-2004631200</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>5.94%→5.43%</t>
+          <t>5.60%→4.93%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>111→104</t>
+          <t>363→330</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>앱클론</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1935813600</v>
+        <v>1168731000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>8.92%→9.12%</t>
+          <t>2.07%→2.48%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>755→797</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="n"/>
-      <c r="H25" s="17" t="n"/>
-      <c r="I25" s="17" t="n"/>
-      <c r="J25" s="17" t="n"/>
-      <c r="K25" s="17" t="n"/>
+          <t>542→613</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>-2697480000</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>10.07%→9.37%</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>242→226</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1747786500</v>
+        <v>1281249900</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>8.45%→8.08%</t>
+          <t>3.11%→3.58%</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>511→540</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="n"/>
-      <c r="H26" s="17" t="n"/>
-      <c r="I26" s="17" t="n"/>
-      <c r="J26" s="17" t="n"/>
-      <c r="K26" s="17" t="n"/>
+          <t>652→715</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>-1179882000</v>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>8.07%→7.55%</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>297→286</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
+          <t>HLB이노베이션</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>423026460</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>1.71%→1.92%</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>1,066→1,127</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>-1481224500</v>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>5.94%→5.41%</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>111→104</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>1935813600</v>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>8.92%→9.04%</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>755→797</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="17" t="n"/>
+      <c r="I28" s="17" t="n"/>
+      <c r="J28" s="17" t="n"/>
+      <c r="K28" s="17" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>1732387500</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>8.45%→7.94%</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>511→540</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="17" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
           <t>보로노이</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B30" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>1207334700</v>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>2.16%→2.77%</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="C30" s="11" t="n">
+        <v>1247372100</v>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>2.16%→2.83%</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>107→120</t>
         </is>
       </c>
-      <c r="G27" s="17" t="n"/>
-      <c r="H27" s="17" t="n"/>
-      <c r="I27" s="17" t="n"/>
-      <c r="J27" s="17" t="n"/>
-      <c r="K27" s="17" t="n"/>
-    </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="19" t="n"/>
-      <c r="G29" s="19" t="n"/>
-      <c r="H29" s="19" t="n"/>
-      <c r="I29" s="19" t="n"/>
-      <c r="J29" s="19" t="n"/>
-      <c r="K29" s="19" t="n"/>
-    </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
-      <c r="G31" s="19" t="n"/>
-      <c r="H31" s="19" t="n"/>
-      <c r="I31" s="19" t="n"/>
-      <c r="J31" s="19" t="n"/>
-      <c r="K31" s="19" t="n"/>
-    </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 294억   ·   현금 14억(4.8%)      주말 2026-08-14  vs  주초 2026-08-10      매수 9종목  /  매도 10종목</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
-      <c r="J33" s="4" t="n"/>
-      <c r="K33" s="4" t="n"/>
+      <c r="G30" s="17" t="n"/>
+      <c r="H30" s="17" t="n"/>
+      <c r="I30" s="17" t="n"/>
+      <c r="J30" s="17" t="n"/>
+      <c r="K30" s="17" t="n"/>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,731억   ·   현금 63억(2.3%)      주말 2026-08-14  vs  주초 2026-08-10      매수 8종목  /  매도 11종목</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="6" t="n"/>
-      <c r="E34" s="6" t="n"/>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="8" t="n"/>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="8" t="n"/>
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J35" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K35" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>PS일렉트로닉스  (신규)</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="C35" s="11" t="n">
+        <v>1178496000</v>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.44%</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>0→150</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>-275</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>-2003760000</v>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>1.34%→0.60%</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>499→224</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>코스맥스엔비티  (신규)</t>
+          <t>미래에셋벤처투자</t>
         </is>
       </c>
       <c r="B36" s="11" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>93276320</v>
+        <v>1521421440</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.33%</t>
+          <t>0.52%→1.14%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>0→122</t>
+          <t>127→250</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>더블유씨피</t>
+          <t>미코</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-194</v>
+        <v>-271</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-132990880</v>
+        <v>-3720288000</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>7.75%→7.30%</t>
+          <t>2.35%→1.27%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>3,246→3,052</t>
+          <t>521→250</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>노바렉스  (신규)</t>
+          <t>한국피아이엠  (신규)</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>60891960</v>
+        <v>3548160000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.21%</t>
+          <t>0.00%→1.31%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>0→51</t>
+          <t>0→80</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-65</v>
+        <v>-230</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-88327200</v>
+        <v>-2948563200</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>1.65%→1.35%</t>
+          <t>1.14%→0.09%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>349→284</t>
+          <t>250→20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>에프앤가이드</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>47002960</v>
+        <v>5529216000</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>3.11%→3.28%</t>
+          <t>1.47%→3.50%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>646→680</t>
+          <t>50→120</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>금양그린파워</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-53</v>
+        <v>-145</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-32707360</v>
+        <v>-3276768000</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>0.81%→0.69%</t>
+          <t>2.54%→1.28%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>375→322</t>
+          <t>298→153</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B39" s="11" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>93423000</v>
+        <v>4227097600</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>7.37%→7.70%</t>
+          <t>1.50%→3.15%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>747→780</t>
+          <t>69→137</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-34</v>
+        <v>-119</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-68734400</v>
+        <v>-2613811200</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>2.80%→2.56%</t>
+          <t>1.96%→0.99%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>397→363</t>
+          <t>241→122</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>한선엔지니어링</t>
+          <t>오킨스전자</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>31786240</v>
+        <v>524113920</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>1.53%→1.64%</t>
+          <t>0.19%→0.40%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>442→474</t>
+          <t>50→97</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>상아프론테크</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-29</v>
+        <v>-77</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-32817560</v>
+        <v>-696572800</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.31%</t>
+          <t>0.38%→0.08%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>107→78</t>
+          <t>101→24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>티에스이  (신규)</t>
         </is>
       </c>
       <c r="B41" s="11" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>71546400</v>
+        <v>3646720000</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>1.99%→2.25%</t>
+          <t>0.00%→1.35%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>72→81</t>
+          <t>0→20</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>씨어스  (편출)</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
-        <v>-18</v>
+        <v>-70</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-49863600</v>
+        <v>-1133440000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>2.60%→2.43%</t>
+          <t>0.47%→0.00%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>269→251</t>
+          <t>70→0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>32056800</v>
+        <v>2756160000</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>2.57%→2.68%</t>
+          <t>1.66%→2.71%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>138→144</t>
+          <t>25→40</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-13</v>
+        <v>-40</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-40656200</v>
+        <v>-2962432000</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>0.75%→0.61%</t>
+          <t>1.90%→0.82%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>69→56</t>
+          <t>70→30</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C43" s="11" t="n">
-        <v>60556800</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>2.88%→3.10%</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>82→88</t>
-        </is>
-      </c>
+      <c r="A43" s="17" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>클래시스</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-8</v>
+        <v>-24</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-26630400</v>
+        <v>-1115136000</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.56%</t>
+          <t>0.46%→0.00%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>56→48</t>
+          <t>24→0</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>실리콘투</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>13756000</v>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>0.87%→0.92%</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>73→77</t>
-        </is>
-      </c>
+      <c r="A44" s="17" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-87020000</v>
+        <v>-982784000</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>2.67%→2.37%</t>
+          <t>1.95%→1.45%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>44→39</t>
+          <t>100→80</t>
         </is>
       </c>
     </row>
@@ -2015,30 +2077,30 @@
       <c r="E45" s="17" t="n"/>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
-        <v>-3</v>
+        <v>-13</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-5791200</v>
+        <v>-1640953600</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>6.59%→6.58%</t>
+          <t>4.55%→5.13%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>980→977</t>
+          <t>123→110</t>
         </is>
       </c>
     </row>
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 596억   ·   현금 20억(3.3%)      주말 2026-08-14  vs  주초 2026-08-10      매수 4종목  /  매도 2종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,349억   ·   현금 45억(1.9%)      주말 2026-08-14  vs  주초 2026-08-10      매수 6종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B47" s="4" t="n"/>
@@ -2127,183 +2189,1037 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>셀트리온제약</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
-        <v>130</v>
+        <v>233</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>524940000</v>
+        <v>3505962650</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>2.56%→3.46%</t>
+          <t>2.63%→4.11%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>368→498</t>
+          <t>400→633</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>휴젤</t>
+          <t>일동제약  (편출)</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-25</v>
+        <v>-400</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-805500000</v>
+        <v>-2065136000</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>5.40%→3.71%</t>
+          <t>0.91%→0.00%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>92→67</t>
+          <t>400→0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>601008000</v>
+        <v>2335410000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>1.37%→2.43%</t>
+          <t>2.41%→3.42%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>103→179</t>
+          <t>201→285</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>네이처셀</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
-        <v>-11</v>
+        <v>-156</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-419100000</v>
+        <v>-1240699200</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>9.81%→9.11%</t>
+          <t>0.67%→0.16%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>150→139</t>
+          <t>202→46</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>앱클론</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>203940000</v>
+        <v>5582068000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>3.36%→3.92%</t>
+          <t>11.00%→13.31%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>559→614</t>
-        </is>
-      </c>
-      <c r="G52" s="17" t="n"/>
-      <c r="H52" s="17" t="n"/>
-      <c r="I52" s="17" t="n"/>
-      <c r="J52" s="17" t="n"/>
-      <c r="K52" s="17" t="n"/>
+          <t>371→453</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-120</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-12839700000</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>16.15%→10.90%</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>356→236</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>1172355600</v>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>0.91%→1.47%</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>99→151</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>HK이노엔  (편출)</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>-102</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>-1429958400</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>0.63%→0.00%</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>102→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>1668150000</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>5.93%→6.10%</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>329→373</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>펩트론  (편출)</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>-1225332000</v>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>0.54%→0.00%</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>20→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
           <t>보로노이</t>
         </is>
       </c>
-      <c r="B53" s="11" t="n">
+      <c r="B55" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>2435836000</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>1.32%→2.63%</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>60→100</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="n"/>
+      <c r="H55" s="17" t="n"/>
+      <c r="I55" s="17" t="n"/>
+      <c r="J55" s="17" t="n"/>
+      <c r="K55" s="17" t="n"/>
+    </row>
+    <row r="57" ht="19" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 294억   ·   현금 14억(4.8%)      주말 2026-08-14  vs  주초 2026-08-10      매수 9종목  /  매도 10종목</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
+      <c r="F57" s="4" t="n"/>
+      <c r="G57" s="4" t="n"/>
+      <c r="H57" s="4" t="n"/>
+      <c r="I57" s="4" t="n"/>
+      <c r="J57" s="4" t="n"/>
+      <c r="K57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="n"/>
+      <c r="I58" s="8" t="n"/>
+      <c r="J58" s="8" t="n"/>
+      <c r="K58" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티  (신규)</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>122</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>93276320</v>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.33%</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>0→122</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>더블유씨피</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-194</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>-132990880</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>7.75%→7.30%</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>3,246→3,052</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>노바렉스  (신규)</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>60891960</v>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.21%</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>0→51</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>-65</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>-88327200</v>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>1.65%→1.35%</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>349→284</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>47002960</v>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>3.11%→3.28%</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>646→680</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>금양그린파워</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>-53</v>
+      </c>
+      <c r="I62" s="15" t="n">
+        <v>-32707360</v>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>0.81%→0.69%</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>375→322</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>93423000</v>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>7.37%→7.70%</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>747→780</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>스피어</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I63" s="15" t="n">
+        <v>-68734400</v>
+      </c>
+      <c r="J63" s="16" t="inlineStr">
+        <is>
+          <t>2.80%→2.56%</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>397→363</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>한선엔지니어링</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>31786240</v>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>1.53%→1.64%</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>442→474</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>상아프론테크</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>-32817560</v>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>0.42%→0.31%</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>107→78</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>71546400</v>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>1.99%→2.25%</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>72→81</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>원익머트리얼즈</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>-49863600</v>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>2.60%→2.43%</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>269→251</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>60556800</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>2.88%→3.10%</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>82→88</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>솔브레인홀딩스</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I66" s="15" t="n">
+        <v>-40656200</v>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>0.75%→0.61%</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>69→56</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>32056800</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>2.57%→2.68%</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>138→144</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>클래시스</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I67" s="15" t="n">
+        <v>-26630400</v>
+      </c>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>0.65%→0.56%</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>56→48</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>13756000</v>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>0.87%→0.92%</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>73→77</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>티씨케이</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I68" s="15" t="n">
+        <v>-87020000</v>
+      </c>
+      <c r="J68" s="16" t="inlineStr">
+        <is>
+          <t>2.67%→2.37%</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="inlineStr">
+        <is>
+          <t>44→39</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="17" t="n"/>
+      <c r="B69" s="17" t="n"/>
+      <c r="C69" s="17" t="n"/>
+      <c r="D69" s="17" t="n"/>
+      <c r="E69" s="17" t="n"/>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I69" s="15" t="n">
+        <v>-5791200</v>
+      </c>
+      <c r="J69" s="16" t="inlineStr">
+        <is>
+          <t>6.59%→6.58%</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>980→977</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="19" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 596억   ·   현금 20억(3.3%)      주말 2026-08-14  vs  주초 2026-08-10      매수 4종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="n"/>
+      <c r="C71" s="4" t="n"/>
+      <c r="D71" s="4" t="n"/>
+      <c r="E71" s="4" t="n"/>
+      <c r="F71" s="4" t="n"/>
+      <c r="G71" s="4" t="n"/>
+      <c r="H71" s="4" t="n"/>
+      <c r="I71" s="4" t="n"/>
+      <c r="J71" s="4" t="n"/>
+      <c r="K71" s="4" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="6" t="n"/>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="n"/>
+      <c r="I72" s="8" t="n"/>
+      <c r="J72" s="8" t="n"/>
+      <c r="K72" s="8" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K73" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>546780000</v>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>2.56%→3.57%</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>368→498</t>
+        </is>
+      </c>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>휴젤</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I74" s="15" t="n">
+        <v>-787500000</v>
+      </c>
+      <c r="J74" s="16" t="inlineStr">
+        <is>
+          <t>5.40%→3.60%</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>92→67</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="n">
+        <v>76</v>
+      </c>
+      <c r="C75" s="11" t="n">
+        <v>610128000</v>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>1.37%→2.45%</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <t>103→179</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I75" s="15" t="n">
+        <v>-419100000</v>
+      </c>
+      <c r="J75" s="16" t="inlineStr">
+        <is>
+          <t>9.81%→9.02%</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="inlineStr">
+        <is>
+          <t>150→139</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>204600000</v>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>3.36%→3.89%</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>559→614</t>
+        </is>
+      </c>
+      <c r="G76" s="17" t="n"/>
+      <c r="H76" s="17" t="n"/>
+      <c r="I76" s="17" t="n"/>
+      <c r="J76" s="17" t="n"/>
+      <c r="K76" s="17" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C53" s="11" t="n">
-        <v>566676000</v>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>1.96%→3.21%</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
+      <c r="C77" s="11" t="n">
+        <v>585468000</v>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>1.96%→3.29%</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
         <is>
           <t>62→89</t>
         </is>
       </c>
-      <c r="G53" s="17" t="n"/>
-      <c r="H53" s="17" t="n"/>
-      <c r="I53" s="17" t="n"/>
-      <c r="J53" s="17" t="n"/>
-      <c r="K53" s="17" t="n"/>
-    </row>
-    <row r="55" ht="19" customHeight="1">
-      <c r="A55" s="18" t="inlineStr">
+      <c r="G77" s="17" t="n"/>
+      <c r="H77" s="17" t="n"/>
+      <c r="I77" s="17" t="n"/>
+      <c r="J77" s="17" t="n"/>
+      <c r="K77" s="17" t="n"/>
+    </row>
+    <row r="79" ht="19" customHeight="1">
+      <c r="A79" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B55" s="19" t="n"/>
-      <c r="C55" s="19" t="n"/>
-      <c r="D55" s="19" t="n"/>
-      <c r="E55" s="19" t="n"/>
-      <c r="F55" s="19" t="n"/>
-      <c r="G55" s="19" t="n"/>
-      <c r="H55" s="19" t="n"/>
-      <c r="I55" s="19" t="n"/>
-      <c r="J55" s="19" t="n"/>
-      <c r="K55" s="19" t="n"/>
+      <c r="B79" s="19" t="n"/>
+      <c r="C79" s="19" t="n"/>
+      <c r="D79" s="19" t="n"/>
+      <c r="E79" s="19" t="n"/>
+      <c r="F79" s="19" t="n"/>
+      <c r="G79" s="19" t="n"/>
+      <c r="H79" s="19" t="n"/>
+      <c r="I79" s="19" t="n"/>
+      <c r="J79" s="19" t="n"/>
+      <c r="K79" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A34:E34"/>
+  <mergeCells count="21">
+    <mergeCell ref="G72:K72"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A79:K79"/>
+    <mergeCell ref="G48:K48"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A57:K57"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="G58:K58"/>
+    <mergeCell ref="A47:K47"/>
+    <mergeCell ref="A71:K71"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="G4:K4"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G34:K34"/>
-    <mergeCell ref="A55:K55"/>
-    <mergeCell ref="A29:K29"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A47:K47"/>
-    <mergeCell ref="G19:K19"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G48:K48"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A31:K31"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="G22:K22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_weekly_20260814.xlsx
+++ b/reports/pdf_weekly_20260814.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,744억   ·   현금 260억(5.3%)      주말 2026-08-14  vs  주초 2026-08-10      매수 11종목  /  매도 14종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,802억   ·   현금 261억(5.3%)      주말 2026-08-14  vs  주초 2026-08-10      매수 11종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>244</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2825715200</v>
+        <v>2839379200</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-285</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-3050041500</v>
+        <v>-3064790250</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>84</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>959758800</v>
+        <v>964399800</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-57</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1880122200</v>
+        <v>-1889213700</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>69</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>4280760000</v>
+        <v>4301460000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-35</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-2279970000</v>
+        <v>-2290995000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>33</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>952003800</v>
+        <v>956607300</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-33</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-3610107600</v>
+        <v>-3627564600</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>433370080</v>
+        <v>435465680</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-31</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-775706800</v>
+        <v>-779457800</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>29</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1889118000</v>
+        <v>1898253000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-19</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1862440800</v>
+        <v>-1871446800</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>973821200</v>
+        <v>978530200</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-15</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-956967000</v>
+        <v>-961594500</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1460835200</v>
+        <v>1467899200</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-13</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-202705360</v>
+        <v>-203685560</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1392177600</v>
+        <v>1398909600</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-2224754400</v>
+        <v>-1311633600</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.78%→0.52%</t>
+          <t>3.87%→3.66%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>25→13</t>
+          <t>168→156</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2142448000</v>
+        <v>2152808000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1305321600</v>
+        <v>-2235512400</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>3.87%→3.66%</t>
+          <t>0.78%→0.52%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>168→156</t>
+          <t>25→13</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1641475000</v>
+        <v>1649412500</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-9</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-821719800</v>
+        <v>-825693300</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>-8</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-303168800</v>
+        <v>-304634800</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>-7</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-555154600</v>
+        <v>-557839100</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>-3</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-809622000</v>
+        <v>-813537000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,037억   ·   현금 21억(0.5%)      주말 2026-08-14  vs  주초 2026-08-10      매수 7종목  /  매도 4종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,051억   ·   현금 21억(0.5%)      주말 2026-08-14  vs  주초 2026-08-10      매수 7종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1575,7 +1575,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,731억   ·   현금 63억(2.3%)      주말 2026-08-14  vs  주초 2026-08-10      매수 8종목  /  매도 11종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,797억   ·   현금 64억(2.3%)      주말 2026-08-14  vs  주초 2026-08-10      매수 8종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1671,7 +1671,7 @@
         <v>150</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1178496000</v>
+        <v>1195236000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>-275</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-2003760000</v>
+        <v>-2032222500</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>123</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1521421440</v>
+        <v>1543032540</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>-271</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-3720288000</v>
+        <v>-3773133000</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>80</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>3548160000</v>
+        <v>3598560000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>-230</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-2948563200</v>
+        <v>-2990446200</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>70</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>5529216000</v>
+        <v>5607756000</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>-145</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-3276768000</v>
+        <v>-3323313000</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>68</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>4227097600</v>
+        <v>4287141600</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>-119</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-2613811200</v>
+        <v>-2650939200</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>47</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>524113920</v>
+        <v>531558720</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>-77</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-696572800</v>
+        <v>-706467300</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>20</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>3646720000</v>
+        <v>3698520000</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>-70</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-1133440000</v>
+        <v>-1149540000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>15</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>2756160000</v>
+        <v>2795310000</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>-40</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-2962432000</v>
+        <v>-3004512000</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>-24</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-1115136000</v>
+        <v>-1130976000</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>-20</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-982784000</v>
+        <v>-996744000</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>-13</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-1640953600</v>
+        <v>-1664262600</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,349억   ·   현금 45억(1.9%)      주말 2026-08-14  vs  주초 2026-08-10      매수 6종목  /  매도 5종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,353억   ·   현금 45억(1.9%)      주말 2026-08-14  vs  주초 2026-08-10      매수 6종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B47" s="4" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>233</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>3505962650</v>
+        <v>3537173000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>-400</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-2065136000</v>
+        <v>-2083520000</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>84</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>2335410000</v>
+        <v>2356200000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>-156</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-1240699200</v>
+        <v>-1251744000</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>82</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>5582068000</v>
+        <v>5631760000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>-120</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-12839700000</v>
+        <v>-12954000000</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>1172355600</v>
+        <v>1182792000</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>-102</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-1429958400</v>
+        <v>-1442688000</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>44</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>1668150000</v>
+        <v>1683000000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>-20</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-1225332000</v>
+        <v>-1236240000</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>40</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>2435836000</v>
+        <v>2457520000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 294억   ·   현금 14억(4.8%)      주말 2026-08-14  vs  주초 2026-08-10      매수 9종목  /  매도 10종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 295억   ·   현금 14억(4.8%)      주말 2026-08-14  vs  주초 2026-08-10      매수 9종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B57" s="4" t="n"/>
@@ -2533,11 +2533,11 @@
         <v>122</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>93276320</v>
+        <v>90772880</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.33%</t>
+          <t>0.00%→0.32%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -2554,11 +2554,11 @@
         <v>-194</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-132990880</v>
+        <v>-136529440</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>7.75%→7.30%</t>
+          <t>7.94%→7.47%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2577,11 +2577,11 @@
         <v>51</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>60891960</v>
+        <v>58450080</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.21%</t>
+          <t>0.00%→0.20%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -2598,11 +2598,11 @@
         <v>-65</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-88327200</v>
+        <v>-88129600</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>1.65%→1.35%</t>
+          <t>1.64%→1.34%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -2621,11 +2621,11 @@
         <v>34</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>47002960</v>
+        <v>47364720</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>3.11%→3.28%</t>
+          <t>3.13%→3.29%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -2642,11 +2642,11 @@
         <v>-53</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-32707360</v>
+        <v>-32183720</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>0.81%→0.69%</t>
+          <t>0.79%→0.68%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -2665,11 +2665,11 @@
         <v>33</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>93423000</v>
+        <v>92670600</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>7.37%→7.70%</t>
+          <t>7.29%→7.62%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
@@ -2686,11 +2686,11 @@
         <v>-34</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-68734400</v>
+        <v>-67054800</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>2.80%→2.56%</t>
+          <t>2.72%→2.49%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -2709,11 +2709,11 @@
         <v>32</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>31786240</v>
+        <v>34242560</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>1.53%→1.64%</t>
+          <t>1.64%→1.76%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -2730,7 +2730,7 @@
         <v>-29</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-32817560</v>
+        <v>-32707360</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
@@ -2753,11 +2753,11 @@
         <v>9</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>71546400</v>
+        <v>72367200</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>1.99%→2.25%</t>
+          <t>2.01%→2.27%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -2774,11 +2774,11 @@
         <v>-18</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-49863600</v>
+        <v>-48632400</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>2.60%→2.43%</t>
+          <t>2.53%→2.36%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
@@ -2790,23 +2790,23 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>60556800</v>
+        <v>34975200</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>2.88%→3.10%</t>
+          <t>2.80%→2.92%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>82→88</t>
+          <t>138→144</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -2818,11 +2818,11 @@
         <v>-13</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-40656200</v>
+        <v>-39767000</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>0.75%→0.61%</t>
+          <t>0.73%→0.60%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
@@ -2834,23 +2834,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>32056800</v>
+        <v>61377600</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>2.57%→2.68%</t>
+          <t>2.92%→3.13%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>138→144</t>
+          <t>82→88</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
@@ -2862,11 +2862,11 @@
         <v>-8</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-26630400</v>
+        <v>-24137600</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.56%</t>
+          <t>0.59%→0.50%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -2885,11 +2885,11 @@
         <v>4</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>13756000</v>
+        <v>12403200</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>0.87%→0.92%</t>
+          <t>0.79%→0.83%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
@@ -2906,11 +2906,11 @@
         <v>-5</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-87020000</v>
+        <v>-86260000</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>2.67%→2.37%</t>
+          <t>2.64%→2.34%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
@@ -2934,11 +2934,11 @@
         <v>-3</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-5791200</v>
+        <v>-5517600</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>6.59%→6.58%</t>
+          <t>6.26%→6.25%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
@@ -2950,7 +2950,7 @@
     <row r="71" ht="19" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 596억   ·   현금 20억(3.3%)      주말 2026-08-14  vs  주초 2026-08-10      매수 4종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 602억   ·   현금 20억(3.3%)      주말 2026-08-14  vs  주초 2026-08-10      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B71" s="4" t="n"/>
@@ -3046,7 +3046,7 @@
         <v>130</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>546780000</v>
+        <v>551336500</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>-25</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-787500000</v>
+        <v>-794062500</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>76</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>610128000</v>
+        <v>615212400</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>-11</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-419100000</v>
+        <v>-422592500</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>55</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>204600000</v>
+        <v>206305000</v>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>27</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>585468000</v>
+        <v>590346900</v>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>

--- a/reports/pdf_weekly_20260814.xlsx
+++ b/reports/pdf_weekly_20260814.xlsx
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1311633600</v>
+        <v>-2235512400</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>3.87%→3.66%</t>
+          <t>0.78%→0.52%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>168→156</t>
+          <t>25→13</t>
         </is>
       </c>
     </row>
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-2235512400</v>
+        <v>-1311633600</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.78%→0.52%</t>
+          <t>3.87%→3.66%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>25→13</t>
+          <t>168→156</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20260814.xlsx
+++ b/reports/pdf_weekly_20260814.xlsx
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-2235512400</v>
+        <v>-1311633600</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.78%→0.52%</t>
+          <t>3.87%→3.66%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>25→13</t>
+          <t>168→156</t>
         </is>
       </c>
     </row>
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1311633600</v>
+        <v>-2235512400</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>3.87%→3.66%</t>
+          <t>0.78%→0.52%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>168→156</t>
+          <t>25→13</t>
         </is>
       </c>
     </row>
@@ -2790,23 +2790,23 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>34975200</v>
+        <v>61377600</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>2.80%→2.92%</t>
+          <t>2.92%→3.13%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>138→144</t>
+          <t>82→88</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -2834,23 +2834,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>61377600</v>
+        <v>34975200</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>2.92%→3.13%</t>
+          <t>2.80%→2.92%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>82→88</t>
+          <t>138→144</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">

--- a/reports/pdf_weekly_20260814.xlsx
+++ b/reports/pdf_weekly_20260814.xlsx
@@ -2790,23 +2790,23 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>61377600</v>
+        <v>34975200</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>2.92%→3.13%</t>
+          <t>2.80%→2.92%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>82→88</t>
+          <t>138→144</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -2834,23 +2834,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>34975200</v>
+        <v>61377600</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>2.80%→2.92%</t>
+          <t>2.92%→3.13%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>138→144</t>
+          <t>82→88</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
